--- a/towers/FPR/DS Provide Decision Support/DS-020/input/data/R3_FutureFlows.xlsx
+++ b/towers/FPR/DS Provide Decision Support/DS-020/input/data/R3_FutureFlows.xlsx
@@ -1713,7 +1713,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="F30" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="G30" t="str">
         <v>Direct</v>
@@ -1751,7 +1751,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="D31" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="E31" t="str">
         <v>ECA-ADLS</v>
@@ -1933,7 +1933,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="F35" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="G35" t="str">
         <v>Direct</v>
@@ -1971,7 +1971,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="D36" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="E36" t="str">
         <v>ECA-ADLS</v>
@@ -2153,7 +2153,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="F40" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="G40" t="str">
         <v>Direct</v>
@@ -2191,7 +2191,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="D41" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="E41" t="str">
         <v>ECA-ADLS</v>
@@ -2373,7 +2373,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="F45" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="G45" t="str">
         <v>Direct</v>
@@ -2411,7 +2411,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="D46" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="E46" t="str">
         <v>ECA-ADLS</v>
@@ -2593,7 +2593,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="F50" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="G50" t="str">
         <v>Direct</v>
@@ -2631,7 +2631,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="D51" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="E51" t="str">
         <v>ECA-ADLS</v>
@@ -2813,7 +2813,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="F55" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="G55" t="str">
         <v>Direct</v>
@@ -2851,7 +2851,7 @@
         <v>Capacity Forecast Data Store</v>
       </c>
       <c r="D56" t="str">
-        <v>ECA Platform</v>
+        <v>Data Warehouse (IE)</v>
       </c>
       <c r="E56" t="str">
         <v>ECA-ADLS</v>

--- a/towers/FPR/DS Provide Decision Support/DS-020/input/data/R3_FutureFlows.xlsx
+++ b/towers/FPR/DS Provide Decision Support/DS-020/input/data/R3_FutureFlows.xlsx
@@ -3136,7 +3136,7 @@
         <v>Snowflake BY</v>
       </c>
       <c r="K62" t="str">
-        <v>Snowflake Cloud DW</v>
+        <v>Snowflake Cloud DW (PDH)</v>
       </c>
       <c r="L62" t="str">
         <v>Blue Yonder Cloud SaaS</v>
@@ -3356,7 +3356,7 @@
         <v>Snowflake BY</v>
       </c>
       <c r="K67" t="str">
-        <v>Snowflake Cloud DW</v>
+        <v>Snowflake Cloud DW (PDH)</v>
       </c>
       <c r="L67" t="str">
         <v>Blue Yonder Cloud SaaS</v>
@@ -3576,7 +3576,7 @@
         <v>Snowflake BY</v>
       </c>
       <c r="K72" t="str">
-        <v>Snowflake Cloud DW</v>
+        <v>Snowflake Cloud DW (PDH)</v>
       </c>
       <c r="L72" t="str">
         <v>Blue Yonder Cloud SaaS</v>
@@ -3796,13 +3796,13 @@
         <v>Snowflake BY</v>
       </c>
       <c r="K77" t="str">
-        <v>Snowflake Cloud DW</v>
+        <v>Snowflake Cloud DW (PDH)</v>
       </c>
       <c r="L77" t="str">
         <v>Blue Yonder Cloud SaaS</v>
       </c>
       <c r="M77" t="str">
-        <v>ECA Platform</v>
+        <v>ECA Azure Platform (PDH)</v>
       </c>
       <c r="N77" t="str">
         <v>Point-to-Point</v>
@@ -4500,7 +4500,7 @@
         <v>SAP HANA Cloud</v>
       </c>
       <c r="K93" t="str">
-        <v>Snowflake Cloud DW</v>
+        <v>Snowflake Cloud DW (PDH)</v>
       </c>
       <c r="L93" t="str">
         <v>SAP HANA Cloud</v>
@@ -4676,7 +4676,7 @@
         <v>SAP HANA Cloud</v>
       </c>
       <c r="K97" t="str">
-        <v>Snowflake Cloud DW</v>
+        <v>Snowflake Cloud DW (PDH)</v>
       </c>
       <c r="L97" t="str">
         <v>SAP HANA Cloud</v>
